--- a/Config/MiniTemplate/Datas/Config/__tables__.xlsx
+++ b/Config/MiniTemplate/Datas/Config/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -110,22 +110,13 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>item.TbItem</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>item.xlsx</t>
-  </si>
-  <si>
-    <t>test.TbReward</t>
-  </si>
-  <si>
-    <t>Reward</t>
-  </si>
-  <si>
-    <t>reward.xlsx</t>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>LanguageInfo</t>
+  </si>
+  <si>
+    <t>language.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1067,8 +1058,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1181,20 +1172,6 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/MiniTemplate/Datas/Config/__tables__.xlsx
+++ b/Config/MiniTemplate/Datas/Config/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -117,6 +117,15 @@
   </si>
   <si>
     <t>language.xlsx</t>
+  </si>
+  <si>
+    <t>RedDot</t>
+  </si>
+  <si>
+    <t>RedDotInfo</t>
+  </si>
+  <si>
+    <t>redDot.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1058,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1172,6 +1181,20 @@
         <v>29</v>
       </c>
     </row>
+    <row r="5" spans="2:5">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
